--- a/Sprint 3/Product Backlog Items 16/sprint_backlog/Sprint backlog card 16.xlsx
+++ b/Sprint 3/Product Backlog Items 16/sprint_backlog/Sprint backlog card 16.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ปี 3\PaiNamNaeWebApp\Sprint 1\sprint_backlog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PaiNamNaeWebAppSec3-3\Sprint 3\Product Backlog Items 16\sprint_backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50928CC5-1EFE-4FFB-9115-F8BFB7710310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C09C81-6872-4BC8-A387-F43D7B93E687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{95F319A4-3021-4B35-9753-B79CED767C2B}"/>
   </bookViews>
@@ -132,9 +132,6 @@
     <t xml:space="preserve">จัดทำ Sprint Backlog </t>
   </si>
   <si>
-    <t>Sprint 1</t>
-  </si>
-  <si>
     <t>Day</t>
   </si>
   <si>
@@ -175,6 +172,9 @@
   </si>
   <si>
     <t>ชนะศักดิ์ กองไชยสงค์นิติภูมิ ยุระรัช</t>
+  </si>
+  <si>
+    <t>Sprint 3</t>
   </si>
 </sst>
 </file>
@@ -374,15 +374,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -400,9 +391,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -420,20 +408,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -450,6 +426,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -457,54 +505,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -882,16 +882,13 @@
                   <a:buFontTx/>
                   <a:buNone/>
                   <a:tabLst/>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr>
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000">
                         <a:lumMod val="65000"/>
                         <a:lumOff val="35000"/>
                       </a:sysClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -1996,11 +1993,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="32.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
     </row>
     <row r="2" spans="1:22" ht="43.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
@@ -2011,64 +2008,64 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="3" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="16" t="s">
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="31.8" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7" t="s">
+      <c r="C4" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="6">
         <v>1</v>
       </c>
-      <c r="H4" s="9">
-        <v>2</v>
-      </c>
-      <c r="I4" s="9">
+      <c r="H4" s="6">
+        <v>2</v>
+      </c>
+      <c r="I4" s="6">
         <v>3</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="6">
         <v>4</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="6">
         <v>5</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="6">
         <v>6</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="6">
         <v>7</v>
       </c>
       <c r="N4" s="2">
@@ -2080,70 +2077,70 @@
       <c r="P4" s="2">
         <v>10</v>
       </c>
-      <c r="Q4" s="27"/>
-      <c r="T4" s="30" t="s">
+      <c r="Q4" s="19"/>
+      <c r="T4" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="U4" s="31" t="s">
+      <c r="V4" s="23" t="s">
         <v>30</v>
-      </c>
-      <c r="V4" s="31" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A5" s="39">
-        <v>1</v>
-      </c>
-      <c r="B5" s="33" t="s">
+      <c r="A5" s="42">
+        <v>3</v>
+      </c>
+      <c r="B5" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="32">
-        <v>2</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="32">
-        <v>2</v>
-      </c>
-      <c r="H5" s="32">
-        <v>0</v>
-      </c>
-      <c r="I5" s="32">
-        <v>0</v>
-      </c>
-      <c r="J5" s="32">
-        <v>0</v>
-      </c>
-      <c r="K5" s="32">
-        <v>0</v>
-      </c>
-      <c r="L5" s="32">
-        <v>0</v>
-      </c>
-      <c r="M5" s="32">
-        <v>0</v>
-      </c>
-      <c r="N5" s="32">
-        <v>0</v>
-      </c>
-      <c r="O5" s="32">
-        <v>0</v>
-      </c>
-      <c r="P5" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="28">
+      <c r="E5" s="24">
+        <v>2</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="24">
+        <v>2</v>
+      </c>
+      <c r="H5" s="24">
+        <v>0</v>
+      </c>
+      <c r="I5" s="24">
+        <v>0</v>
+      </c>
+      <c r="J5" s="24">
+        <v>0</v>
+      </c>
+      <c r="K5" s="24">
+        <v>0</v>
+      </c>
+      <c r="L5" s="24">
+        <v>0</v>
+      </c>
+      <c r="M5" s="24">
+        <v>0</v>
+      </c>
+      <c r="N5" s="24">
+        <v>0</v>
+      </c>
+      <c r="O5" s="24">
+        <v>0</v>
+      </c>
+      <c r="P5" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="20">
         <v>3</v>
       </c>
-      <c r="T5" s="30"/>
+      <c r="T5" s="22"/>
       <c r="U5" s="1">
         <v>1</v>
       </c>
@@ -2152,52 +2149,52 @@
       </c>
     </row>
     <row r="6" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A6" s="40"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="19" t="s">
+      <c r="A6" s="43"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="32">
+      <c r="D6" s="47"/>
+      <c r="E6" s="24">
         <v>3</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="32">
+      <c r="F6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="24">
         <v>3</v>
       </c>
-      <c r="H6" s="32">
-        <v>0</v>
-      </c>
-      <c r="I6" s="32">
-        <v>0</v>
-      </c>
-      <c r="J6" s="32">
-        <v>0</v>
-      </c>
-      <c r="K6" s="32">
-        <v>0</v>
-      </c>
-      <c r="L6" s="32">
-        <v>0</v>
-      </c>
-      <c r="M6" s="32">
-        <v>0</v>
-      </c>
-      <c r="N6" s="32">
-        <v>0</v>
-      </c>
-      <c r="O6" s="32">
-        <v>0</v>
-      </c>
-      <c r="P6" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="28">
+      <c r="H6" s="24">
+        <v>0</v>
+      </c>
+      <c r="I6" s="24">
+        <v>0</v>
+      </c>
+      <c r="J6" s="24">
+        <v>0</v>
+      </c>
+      <c r="K6" s="24">
+        <v>0</v>
+      </c>
+      <c r="L6" s="24">
+        <v>0</v>
+      </c>
+      <c r="M6" s="24">
+        <v>0</v>
+      </c>
+      <c r="N6" s="24">
+        <v>0</v>
+      </c>
+      <c r="O6" s="24">
+        <v>0</v>
+      </c>
+      <c r="P6" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="20">
         <v>5</v>
       </c>
-      <c r="T6" s="30"/>
+      <c r="T6" s="22"/>
       <c r="U6" s="1">
         <v>2</v>
       </c>
@@ -2206,52 +2203,52 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A7" s="40"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="19" t="s">
+      <c r="A7" s="43"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="32">
-        <v>2</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="32">
-        <v>2</v>
-      </c>
-      <c r="H7" s="32">
-        <v>0</v>
-      </c>
-      <c r="I7" s="32">
-        <v>0</v>
-      </c>
-      <c r="J7" s="32">
-        <v>0</v>
-      </c>
-      <c r="K7" s="32">
-        <v>0</v>
-      </c>
-      <c r="L7" s="32">
-        <v>0</v>
-      </c>
-      <c r="M7" s="32">
-        <v>0</v>
-      </c>
-      <c r="N7" s="32">
-        <v>0</v>
-      </c>
-      <c r="O7" s="32">
-        <v>0</v>
-      </c>
-      <c r="P7" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="28">
+      <c r="D7" s="47"/>
+      <c r="E7" s="24">
+        <v>2</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="24">
+        <v>2</v>
+      </c>
+      <c r="H7" s="24">
+        <v>0</v>
+      </c>
+      <c r="I7" s="24">
+        <v>0</v>
+      </c>
+      <c r="J7" s="24">
+        <v>0</v>
+      </c>
+      <c r="K7" s="24">
+        <v>0</v>
+      </c>
+      <c r="L7" s="24">
+        <v>0</v>
+      </c>
+      <c r="M7" s="24">
+        <v>0</v>
+      </c>
+      <c r="N7" s="24">
+        <v>0</v>
+      </c>
+      <c r="O7" s="24">
+        <v>0</v>
+      </c>
+      <c r="P7" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="20">
         <v>6</v>
       </c>
-      <c r="T7" s="30"/>
+      <c r="T7" s="22"/>
       <c r="U7" s="1">
         <v>3</v>
       </c>
@@ -2260,52 +2257,52 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A8" s="40"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="19" t="s">
+      <c r="A8" s="43"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="32">
+      <c r="D8" s="47"/>
+      <c r="E8" s="24">
         <v>4</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="32">
+      <c r="F8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="24">
         <v>4</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="24">
         <v>4</v>
       </c>
-      <c r="I8" s="32">
-        <v>0</v>
-      </c>
-      <c r="J8" s="32">
-        <v>0</v>
-      </c>
-      <c r="K8" s="32">
-        <v>0</v>
-      </c>
-      <c r="L8" s="32">
-        <v>0</v>
-      </c>
-      <c r="M8" s="32">
-        <v>0</v>
-      </c>
-      <c r="N8" s="32">
-        <v>0</v>
-      </c>
-      <c r="O8" s="32">
-        <v>0</v>
-      </c>
-      <c r="P8" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="28">
+      <c r="I8" s="24">
+        <v>0</v>
+      </c>
+      <c r="J8" s="24">
+        <v>0</v>
+      </c>
+      <c r="K8" s="24">
+        <v>0</v>
+      </c>
+      <c r="L8" s="24">
+        <v>0</v>
+      </c>
+      <c r="M8" s="24">
+        <v>0</v>
+      </c>
+      <c r="N8" s="24">
+        <v>0</v>
+      </c>
+      <c r="O8" s="24">
+        <v>0</v>
+      </c>
+      <c r="P8" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="20">
         <v>10</v>
       </c>
-      <c r="T8" s="30"/>
+      <c r="T8" s="22"/>
       <c r="U8" s="1">
         <v>4</v>
       </c>
@@ -2314,52 +2311,52 @@
       </c>
     </row>
     <row r="9" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A9" s="41"/>
-      <c r="B9" s="35"/>
-      <c r="C9" s="19" t="s">
+      <c r="A9" s="44"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="42">
-        <v>2</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="32">
-        <v>2</v>
-      </c>
-      <c r="H9" s="43">
-        <v>2</v>
-      </c>
-      <c r="I9" s="32">
-        <v>2</v>
-      </c>
-      <c r="J9" s="32">
-        <v>0</v>
-      </c>
-      <c r="K9" s="32">
-        <v>0</v>
-      </c>
-      <c r="L9" s="32">
-        <v>0</v>
-      </c>
-      <c r="M9" s="32">
-        <v>0</v>
-      </c>
-      <c r="N9" s="32">
-        <v>0</v>
-      </c>
-      <c r="O9" s="32">
-        <v>0</v>
-      </c>
-      <c r="P9" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="28">
+      <c r="D9" s="48"/>
+      <c r="E9" s="25">
+        <v>2</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="24">
+        <v>2</v>
+      </c>
+      <c r="H9" s="26">
+        <v>2</v>
+      </c>
+      <c r="I9" s="24">
+        <v>2</v>
+      </c>
+      <c r="J9" s="24">
+        <v>0</v>
+      </c>
+      <c r="K9" s="24">
+        <v>0</v>
+      </c>
+      <c r="L9" s="24">
+        <v>0</v>
+      </c>
+      <c r="M9" s="24">
+        <v>0</v>
+      </c>
+      <c r="N9" s="24">
+        <v>0</v>
+      </c>
+      <c r="O9" s="24">
+        <v>0</v>
+      </c>
+      <c r="P9" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="20">
         <v>3</v>
       </c>
-      <c r="T9" s="30"/>
+      <c r="T9" s="22"/>
       <c r="U9" s="1">
         <v>5</v>
       </c>
@@ -2368,58 +2365,58 @@
       </c>
     </row>
     <row r="10" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A10" s="36">
-        <v>1</v>
-      </c>
-      <c r="B10" s="36" t="s">
+      <c r="A10" s="39">
+        <v>3</v>
+      </c>
+      <c r="B10" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="21" t="s">
+      <c r="C10" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="13">
         <v>3</v>
       </c>
-      <c r="F10" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="32">
+      <c r="F10" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="24">
         <v>3</v>
       </c>
-      <c r="H10" s="43">
-        <v>0</v>
-      </c>
-      <c r="I10" s="32">
-        <v>0</v>
-      </c>
-      <c r="J10" s="32">
-        <v>0</v>
-      </c>
-      <c r="K10" s="32">
-        <v>0</v>
-      </c>
-      <c r="L10" s="32">
-        <v>0</v>
-      </c>
-      <c r="M10" s="32">
-        <v>0</v>
-      </c>
-      <c r="N10" s="32">
-        <v>0</v>
-      </c>
-      <c r="O10" s="32">
-        <v>0</v>
-      </c>
-      <c r="P10" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="28">
+      <c r="H10" s="26">
+        <v>0</v>
+      </c>
+      <c r="I10" s="24">
+        <v>0</v>
+      </c>
+      <c r="J10" s="24">
+        <v>0</v>
+      </c>
+      <c r="K10" s="24">
+        <v>0</v>
+      </c>
+      <c r="L10" s="24">
+        <v>0</v>
+      </c>
+      <c r="M10" s="24">
+        <v>0</v>
+      </c>
+      <c r="N10" s="24">
+        <v>0</v>
+      </c>
+      <c r="O10" s="24">
+        <v>0</v>
+      </c>
+      <c r="P10" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="20">
         <v>4</v>
       </c>
-      <c r="T10" s="30"/>
+      <c r="T10" s="22"/>
       <c r="U10" s="1">
         <v>6</v>
       </c>
@@ -2428,52 +2425,52 @@
       </c>
     </row>
     <row r="11" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A11" s="37"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="15" t="s">
+      <c r="A11" s="40"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="42">
+      <c r="D11" s="47"/>
+      <c r="E11" s="25">
         <v>11</v>
       </c>
-      <c r="F11" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="46">
+      <c r="F11" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="29">
         <v>11</v>
       </c>
-      <c r="H11" s="43">
+      <c r="H11" s="26">
         <v>11</v>
       </c>
-      <c r="I11" s="32">
+      <c r="I11" s="24">
         <v>11</v>
       </c>
-      <c r="J11" s="32">
+      <c r="J11" s="24">
         <v>11</v>
       </c>
-      <c r="K11" s="32">
-        <v>0</v>
-      </c>
-      <c r="L11" s="32">
-        <v>0</v>
-      </c>
-      <c r="M11" s="32">
-        <v>0</v>
-      </c>
-      <c r="N11" s="32">
-        <v>0</v>
-      </c>
-      <c r="O11" s="32">
-        <v>0</v>
-      </c>
-      <c r="P11" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="28">
+      <c r="K11" s="24">
+        <v>0</v>
+      </c>
+      <c r="L11" s="24">
+        <v>0</v>
+      </c>
+      <c r="M11" s="24">
+        <v>0</v>
+      </c>
+      <c r="N11" s="24">
+        <v>0</v>
+      </c>
+      <c r="O11" s="24">
+        <v>0</v>
+      </c>
+      <c r="P11" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="20">
         <v>11</v>
       </c>
-      <c r="T11" s="30"/>
+      <c r="T11" s="22"/>
       <c r="U11" s="1">
         <v>7</v>
       </c>
@@ -2482,52 +2479,52 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="15" t="s">
+      <c r="A12" s="40"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="42">
+      <c r="D12" s="47"/>
+      <c r="E12" s="25">
         <v>6</v>
       </c>
-      <c r="F12" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="32">
+      <c r="F12" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="24">
         <v>6</v>
       </c>
-      <c r="H12" s="43">
+      <c r="H12" s="26">
         <v>6</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="24">
         <v>6</v>
       </c>
-      <c r="J12" s="32">
-        <v>0</v>
-      </c>
-      <c r="K12" s="32">
-        <v>0</v>
-      </c>
-      <c r="L12" s="32">
-        <v>0</v>
-      </c>
-      <c r="M12" s="32">
-        <v>0</v>
-      </c>
-      <c r="N12" s="32">
-        <v>0</v>
-      </c>
-      <c r="O12" s="32">
-        <v>0</v>
-      </c>
-      <c r="P12" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="28">
+      <c r="J12" s="24">
+        <v>0</v>
+      </c>
+      <c r="K12" s="24">
+        <v>0</v>
+      </c>
+      <c r="L12" s="24">
+        <v>0</v>
+      </c>
+      <c r="M12" s="24">
+        <v>0</v>
+      </c>
+      <c r="N12" s="24">
+        <v>0</v>
+      </c>
+      <c r="O12" s="24">
+        <v>0</v>
+      </c>
+      <c r="P12" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="20">
         <v>4</v>
       </c>
-      <c r="T12" s="30"/>
+      <c r="T12" s="22"/>
       <c r="U12" s="1">
         <v>8</v>
       </c>
@@ -2536,52 +2533,52 @@
       </c>
     </row>
     <row r="13" spans="1:22" ht="59.4" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A13" s="38"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="20" t="s">
+      <c r="A13" s="41"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="42">
+      <c r="D13" s="48"/>
+      <c r="E13" s="25">
         <v>3</v>
       </c>
-      <c r="F13" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="46">
+      <c r="F13" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="29">
         <v>4</v>
       </c>
-      <c r="H13" s="43">
-        <v>0</v>
-      </c>
-      <c r="I13" s="32">
-        <v>0</v>
-      </c>
-      <c r="J13" s="32">
-        <v>0</v>
-      </c>
-      <c r="K13" s="32">
-        <v>0</v>
-      </c>
-      <c r="L13" s="32">
-        <v>0</v>
-      </c>
-      <c r="M13" s="32">
-        <v>0</v>
-      </c>
-      <c r="N13" s="32">
-        <v>0</v>
-      </c>
-      <c r="O13" s="32">
-        <v>0</v>
-      </c>
-      <c r="P13" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="28">
+      <c r="H13" s="26">
+        <v>0</v>
+      </c>
+      <c r="I13" s="24">
+        <v>0</v>
+      </c>
+      <c r="J13" s="24">
+        <v>0</v>
+      </c>
+      <c r="K13" s="24">
+        <v>0</v>
+      </c>
+      <c r="L13" s="24">
+        <v>0</v>
+      </c>
+      <c r="M13" s="24">
+        <v>0</v>
+      </c>
+      <c r="N13" s="24">
+        <v>0</v>
+      </c>
+      <c r="O13" s="24">
+        <v>0</v>
+      </c>
+      <c r="P13" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="20">
         <v>4</v>
       </c>
-      <c r="T13" s="30"/>
+      <c r="T13" s="22"/>
       <c r="U13" s="1">
         <v>9</v>
       </c>
@@ -2590,58 +2587,58 @@
       </c>
     </row>
     <row r="14" spans="1:22" ht="59.4" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A14" s="25">
-        <v>1</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="45">
+        <v>3</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="6">
+      <c r="D14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="3">
         <v>8</v>
       </c>
-      <c r="F14" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="32">
+      <c r="F14" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="24">
         <v>8</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="24">
         <v>8</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="24">
         <v>8</v>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="24">
         <v>8</v>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="24">
         <v>8</v>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="24">
         <v>8</v>
       </c>
-      <c r="M14" s="32">
-        <v>0</v>
-      </c>
-      <c r="N14" s="32">
-        <v>0</v>
-      </c>
-      <c r="O14" s="32">
-        <v>0</v>
-      </c>
-      <c r="P14" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="29">
+      <c r="M14" s="24">
+        <v>0</v>
+      </c>
+      <c r="N14" s="24">
+        <v>0</v>
+      </c>
+      <c r="O14" s="24">
+        <v>0</v>
+      </c>
+      <c r="P14" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="21">
         <v>7</v>
       </c>
-      <c r="T14" s="30"/>
+      <c r="T14" s="22"/>
       <c r="U14" s="1">
         <v>10</v>
       </c>
@@ -2650,383 +2647,384 @@
       </c>
     </row>
     <row r="15" spans="1:22" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="25"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="24" t="s">
+      <c r="A15" s="45"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="6">
-        <v>2</v>
-      </c>
-      <c r="F15" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="32">
-        <v>2</v>
-      </c>
-      <c r="H15" s="32">
-        <v>2</v>
-      </c>
-      <c r="I15" s="32">
-        <v>2</v>
-      </c>
-      <c r="J15" s="32">
-        <v>2</v>
-      </c>
-      <c r="K15" s="32">
-        <v>2</v>
-      </c>
-      <c r="L15" s="32">
-        <v>2</v>
-      </c>
-      <c r="M15" s="32">
-        <v>0</v>
-      </c>
-      <c r="N15" s="32">
-        <v>0</v>
-      </c>
-      <c r="O15" s="32">
-        <v>0</v>
-      </c>
-      <c r="P15" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="28">
+      <c r="E15" s="3">
+        <v>2</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="24">
+        <v>2</v>
+      </c>
+      <c r="H15" s="24">
+        <v>2</v>
+      </c>
+      <c r="I15" s="24">
+        <v>2</v>
+      </c>
+      <c r="J15" s="24">
+        <v>2</v>
+      </c>
+      <c r="K15" s="24">
+        <v>2</v>
+      </c>
+      <c r="L15" s="24">
+        <v>2</v>
+      </c>
+      <c r="M15" s="24">
+        <v>0</v>
+      </c>
+      <c r="N15" s="24">
+        <v>0</v>
+      </c>
+      <c r="O15" s="24">
+        <v>0</v>
+      </c>
+      <c r="P15" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="6">
+      <c r="A16" s="45"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="45"/>
+      <c r="E16" s="3">
         <v>1</v>
       </c>
-      <c r="F16" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="32">
+      <c r="F16" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="24">
         <v>1</v>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="24">
         <v>1</v>
       </c>
-      <c r="I16" s="32">
+      <c r="I16" s="24">
         <v>1</v>
       </c>
-      <c r="J16" s="32">
+      <c r="J16" s="24">
         <v>1</v>
       </c>
-      <c r="K16" s="32">
+      <c r="K16" s="24">
         <v>1</v>
       </c>
-      <c r="L16" s="32">
+      <c r="L16" s="24">
         <v>1</v>
       </c>
-      <c r="M16" s="32">
-        <v>0</v>
-      </c>
-      <c r="N16" s="32">
-        <v>0</v>
-      </c>
-      <c r="O16" s="32">
-        <v>0</v>
-      </c>
-      <c r="P16" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="28">
+      <c r="M16" s="24">
+        <v>0</v>
+      </c>
+      <c r="N16" s="24">
+        <v>0</v>
+      </c>
+      <c r="O16" s="24">
+        <v>0</v>
+      </c>
+      <c r="P16" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="26" t="s">
+      <c r="A17" s="45"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="6">
-        <v>2</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="32">
-        <v>2</v>
-      </c>
-      <c r="H17" s="32">
-        <v>2</v>
-      </c>
-      <c r="I17" s="32">
-        <v>2</v>
-      </c>
-      <c r="J17" s="32">
-        <v>2</v>
-      </c>
-      <c r="K17" s="32">
-        <v>2</v>
-      </c>
-      <c r="L17" s="32">
-        <v>2</v>
-      </c>
-      <c r="M17" s="32">
-        <v>0</v>
-      </c>
-      <c r="N17" s="32">
-        <v>0</v>
-      </c>
-      <c r="O17" s="32">
-        <v>0</v>
-      </c>
-      <c r="P17" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="28">
+      <c r="E17" s="3">
+        <v>2</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="24">
+        <v>2</v>
+      </c>
+      <c r="H17" s="24">
+        <v>2</v>
+      </c>
+      <c r="I17" s="24">
+        <v>2</v>
+      </c>
+      <c r="J17" s="24">
+        <v>2</v>
+      </c>
+      <c r="K17" s="24">
+        <v>2</v>
+      </c>
+      <c r="L17" s="24">
+        <v>2</v>
+      </c>
+      <c r="M17" s="24">
+        <v>0</v>
+      </c>
+      <c r="N17" s="24">
+        <v>0</v>
+      </c>
+      <c r="O17" s="24">
+        <v>0</v>
+      </c>
+      <c r="P17" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="25"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="24" t="s">
+      <c r="A18" s="45"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="6">
+      <c r="D18" s="47"/>
+      <c r="E18" s="3">
         <v>3</v>
       </c>
-      <c r="F18" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="G18" s="44">
+      <c r="F18" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="27">
         <v>3</v>
       </c>
-      <c r="H18" s="44">
+      <c r="H18" s="27">
         <v>3</v>
       </c>
-      <c r="I18" s="32">
+      <c r="I18" s="24">
         <v>3</v>
       </c>
-      <c r="J18" s="32">
+      <c r="J18" s="24">
         <v>3</v>
       </c>
-      <c r="K18" s="32">
+      <c r="K18" s="24">
         <v>3</v>
       </c>
-      <c r="L18" s="32">
+      <c r="L18" s="24">
         <v>3</v>
       </c>
-      <c r="M18" s="32">
-        <v>0</v>
-      </c>
-      <c r="N18" s="32">
-        <v>0</v>
-      </c>
-      <c r="O18" s="32">
-        <v>0</v>
-      </c>
-      <c r="P18" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="28">
+      <c r="M18" s="24">
+        <v>0</v>
+      </c>
+      <c r="N18" s="24">
+        <v>0</v>
+      </c>
+      <c r="O18" s="24">
+        <v>0</v>
+      </c>
+      <c r="P18" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="20">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="25"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17">
+      <c r="A19" s="45"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="47"/>
+      <c r="E19" s="13">
         <v>1</v>
       </c>
-      <c r="F19" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" s="46">
+      <c r="F19" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="29">
         <v>1</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="24">
         <v>1</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="24">
         <v>1</v>
       </c>
-      <c r="J19" s="32">
+      <c r="J19" s="24">
         <v>1</v>
       </c>
-      <c r="K19" s="32">
+      <c r="K19" s="24">
         <v>1</v>
       </c>
-      <c r="L19" s="32">
+      <c r="L19" s="24">
         <v>1</v>
       </c>
-      <c r="M19" s="32">
-        <v>0</v>
-      </c>
-      <c r="N19" s="32">
-        <v>0</v>
-      </c>
-      <c r="O19" s="32">
-        <v>0</v>
-      </c>
-      <c r="P19" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="28">
+      <c r="M19" s="24">
+        <v>0</v>
+      </c>
+      <c r="N19" s="24">
+        <v>0</v>
+      </c>
+      <c r="O19" s="24">
+        <v>0</v>
+      </c>
+      <c r="P19" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="20">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="59.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17">
-        <v>2</v>
-      </c>
-      <c r="F20" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="46">
-        <v>2</v>
-      </c>
-      <c r="H20" s="32">
-        <v>2</v>
-      </c>
-      <c r="I20" s="32">
-        <v>2</v>
-      </c>
-      <c r="J20" s="32">
-        <v>2</v>
-      </c>
-      <c r="K20" s="32">
-        <v>2</v>
-      </c>
-      <c r="L20" s="32">
-        <v>2</v>
-      </c>
-      <c r="M20" s="32">
-        <v>0</v>
-      </c>
-      <c r="N20" s="32">
-        <v>0</v>
-      </c>
-      <c r="O20" s="32">
-        <v>0</v>
-      </c>
-      <c r="P20" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="28">
+      <c r="A20" s="45"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="47"/>
+      <c r="E20" s="13">
+        <v>2</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="29">
+        <v>2</v>
+      </c>
+      <c r="H20" s="24">
+        <v>2</v>
+      </c>
+      <c r="I20" s="24">
+        <v>2</v>
+      </c>
+      <c r="J20" s="24">
+        <v>2</v>
+      </c>
+      <c r="K20" s="24">
+        <v>2</v>
+      </c>
+      <c r="L20" s="24">
+        <v>2</v>
+      </c>
+      <c r="M20" s="24">
+        <v>0</v>
+      </c>
+      <c r="N20" s="24">
+        <v>0</v>
+      </c>
+      <c r="O20" s="24">
+        <v>0</v>
+      </c>
+      <c r="P20" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="52.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="24" t="s">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="48"/>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="6">
+      <c r="G21" s="28">
         <v>1</v>
       </c>
-      <c r="F21" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" s="45">
+      <c r="H21" s="28">
         <v>1</v>
       </c>
-      <c r="H21" s="45">
+      <c r="I21" s="24">
         <v>1</v>
       </c>
-      <c r="I21" s="32">
+      <c r="J21" s="24">
         <v>1</v>
       </c>
-      <c r="J21" s="32">
+      <c r="K21" s="24">
         <v>1</v>
       </c>
-      <c r="K21" s="32">
+      <c r="L21" s="24">
         <v>1</v>
       </c>
-      <c r="L21" s="32">
-        <v>1</v>
-      </c>
-      <c r="M21" s="32">
-        <v>0</v>
-      </c>
-      <c r="N21" s="32">
-        <v>0</v>
-      </c>
-      <c r="O21" s="32">
-        <v>0</v>
-      </c>
-      <c r="P21" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="28">
+      <c r="M21" s="24">
+        <v>0</v>
+      </c>
+      <c r="N21" s="24">
+        <v>0</v>
+      </c>
+      <c r="O21" s="24">
+        <v>0</v>
+      </c>
+      <c r="P21" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="20">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="G22" s="14">
+      <c r="G22" s="10">
         <f>SUM(G5:G21)</f>
         <v>57</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="10">
         <f t="shared" ref="H22:L22" si="0">SUM(H5:H21)</f>
         <v>43</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="10">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="10">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="10">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="10">
         <f>SUM(M5:M20)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="14">
-        <v>0</v>
-      </c>
-      <c r="O22" s="14">
-        <v>0</v>
-      </c>
-      <c r="P22" s="47">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="14">
+      <c r="N22" s="10">
+        <v>0</v>
+      </c>
+      <c r="O22" s="10">
+        <v>0</v>
+      </c>
+      <c r="P22" s="30">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="10">
         <f>SUM(Q5:Q21)</f>
         <v>71</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:D1"/>
     <mergeCell ref="G3:P3"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A5:A9"/>
@@ -3037,7 +3035,6 @@
     <mergeCell ref="D5:D9"/>
     <mergeCell ref="B5:B9"/>
     <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B1:D1"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="70" orientation="landscape" r:id="rId1"/>
